--- a/dataset/construct/dataset_splits/data_size/5_percent/lmu/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/lmu/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54470472</v>
+        <v>52919815</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,74 +625,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>89.39630390143741</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>79.49349760438059</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.8373702422145</v>
+      </c>
       <c r="E2" t="n">
-        <v>27.9903628117914</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="I2" t="n">
+        <v>146</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>227</v>
+      </c>
+      <c r="K2" t="n">
+        <v>673</v>
+      </c>
+      <c r="L2" t="n">
+        <v>294</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39</v>
+      </c>
       <c r="O2" t="n">
-        <v>518</v>
+        <v>366</v>
       </c>
       <c r="P2" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>0.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.74591750931078</v>
       </c>
       <c r="X2" t="n">
-        <v>26.9</v>
+        <v>22.84236339419522</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>88.5</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -724,25 +723,12 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>110</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52511121</v>
+        <v>54990446</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -750,117 +736,106 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84.0876112251882</v>
+        <v>79.17590691307321</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>29.8605512257756</v>
       </c>
       <c r="E3" t="n">
-        <v>29.1363163371488</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>40</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>419</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>439</v>
+        <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="N3" t="n">
-        <v>1173</v>
+        <v>82</v>
       </c>
       <c r="O3" t="n">
-        <v>419</v>
+        <v>339</v>
       </c>
       <c r="P3" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1139</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>221</v>
+        <v>30.4</v>
       </c>
       <c r="V3" t="n">
-        <v>394</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>30.08028424436822</v>
       </c>
       <c r="X3" t="n">
-        <v>28.8</v>
+        <v>29.51741554510272</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>90.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>629.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52011910</v>
+        <v>52772610</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -868,105 +843,110 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.8980150581793</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>82.2313483915127</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.3417582863402</v>
+      </c>
       <c r="E4" t="n">
-        <v>16.5289256198347</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>622</v>
+      </c>
+      <c r="I4" t="n">
+        <v>632</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>653</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1907</v>
+      </c>
+      <c r="L4" t="n">
+        <v>622</v>
+      </c>
+      <c r="M4" t="n">
+        <v>431</v>
+      </c>
+      <c r="N4" t="n">
+        <v>622</v>
+      </c>
       <c r="O4" t="n">
-        <v>340.14984</v>
+        <v>1675</v>
       </c>
       <c r="P4" t="n">
-        <v>38.76126</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.43289</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>411.34402</v>
+        <v>88</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>32.34028443627313</v>
       </c>
       <c r="X4" t="n">
-        <v>21.753738</v>
+        <v>30.52886088189566</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>69.67747</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>371.27145</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55642168</v>
+        <v>54767222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -974,77 +954,83 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.4695414099932</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>82.7186858316222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>27.7322997761369</v>
+      </c>
       <c r="E5" t="n">
-        <v>24.5778671518401</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56</v>
+      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>55</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>428</v>
+      </c>
+      <c r="M5" t="n">
+        <v>123</v>
+      </c>
+      <c r="N5" t="n">
+        <v>143</v>
+      </c>
       <c r="O5" t="n">
-        <v>435.7692</v>
+        <v>694</v>
       </c>
       <c r="P5" t="n">
-        <v>471.15186</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>348.57095</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1255.492</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>175</v>
+        <v>27.7</v>
       </c>
       <c r="V5" t="n">
-        <v>226</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>27.69296009798979</v>
       </c>
       <c r="X5" t="n">
-        <v>27.29889</v>
+        <v>27.27785163723912</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>86.90398999999999</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>573.0519</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1053,30 +1039,21 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53959319</v>
+        <v>51549417</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1084,70 +1061,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.8637919233402</v>
+        <v>69.864476386037</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>24.2122933884297</v>
       </c>
       <c r="E6" t="n">
-        <v>24.7251829329413</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>48</v>
+      </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>781</v>
+      </c>
+      <c r="I6" t="n">
+        <v>641</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>735</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2157</v>
+      </c>
+      <c r="L6" t="n">
+        <v>774</v>
+      </c>
+      <c r="M6" t="n">
+        <v>351</v>
+      </c>
+      <c r="N6" t="n">
+        <v>595</v>
+      </c>
       <c r="O6" t="n">
-        <v>331</v>
+        <v>1720</v>
       </c>
       <c r="P6" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>641</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>28.17042492726548</v>
       </c>
       <c r="X6" t="n">
-        <v>24.1</v>
+        <v>27.44305359669089</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>79.8</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>471.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1156,39 +1145,30 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>145</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52714540</v>
+        <v>54514630</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1196,77 +1176,71 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.2313483915127</v>
+        <v>82.2915811088296</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>27.8851873884593</v>
       </c>
       <c r="E7" t="n">
-        <v>30.7933824417341</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>402</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="M7" t="n">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="N7" t="n">
-        <v>833</v>
+        <v>131</v>
       </c>
       <c r="O7" t="n">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="P7" t="n">
-        <v>175</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>833</v>
+        <v>102</v>
       </c>
       <c r="S7" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="V7" t="n">
-        <v>36</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>24.06422739549457</v>
       </c>
       <c r="X7" t="n">
-        <v>30.4</v>
+        <v>23.49902105517675</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>98.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>700.4</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1284,28 +1258,19 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>127</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
